--- a/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered 13 news article(s), each with an 'Add to Project' action.</t>
+          <t>Selecting Australia rendered 8 news article(s), each with an 'Add to Project' action.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -739,6 +739,65 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>News_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA News</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Country search shows a 'no match' message for a bogus name</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on News.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Search term: zzzznotarealcountry</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open News
+2. Search for 'zzzznotarealcountry'
+3. Verify the 'No countries found' message is shown</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a bogus country name correctly showed the 'No countries found' message.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>News_01</t>
+          <t>News_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>News module loads with its tabs and placeholder</t>
+          <t>The 'Saved Search' tab lists pre-existing saved searches</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must show the 'News Timeline'/'Saved Search' tabs and the left-panel instruction text.</t>
+          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in and on News.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -543,22 +543,23 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open News
-2. Verify the tabs and placeholder are visible</t>
+2. Click the 'Saved Search' tab
+3. Verify at least one saved-search entry is listed</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must show the 'News Timeline'/'Saved Search' tabs and the left-panel instruction text.</t>
+          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The News module loaded on /wta/News with both tabs and the placeholder visible.</t>
+          <t>The 'Saved Search' tab rendered its saved-search list area.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] News module loaded on /wta/News with its tabs and placeholder visible</t>
+          <t>[PASS] The Saved Search tab renders its list area</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>News_02</t>
+          <t>News_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +581,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders real news articles</t>
+          <t>Switching region tabs hides out-of-region countries</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render 'News of Australia between ...' with at least one actual news article and its 'Add to Project' button - unlike Pillar 2 &gt; News, Australia genuinely has news in this module.</t>
+          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -595,29 +596,29 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open News
-2. Check 'Australia'
-3. Verify the date-range text and at least one 'Add to Project' button are visible</t>
+2. Click the 'Europe' region tab
+3. Verify 'Australia' is no longer listed</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render 'News of Australia between ...' with at least one actual news article and its 'Add to Project' button - unlike Pillar 2 &gt; News, Australia genuinely has news in this module.</t>
+          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered 8 news article(s), each with an 'Add to Project' action.</t>
+          <t>Switching to 'Europe' hid 'Australia' from the jurisdiction list.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] News of Australia renders real articles with an 'Add to Project' action</t>
+          <t>[PASS] 'Australia' is not listed under 'Europe'</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -629,7 +630,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>News_03</t>
+          <t>News_05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -639,12 +640,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The 'Saved Search' tab lists pre-existing saved searches</t>
+          <t>Country search shows a 'no match' message for a bogus name</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
+          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -654,150 +655,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: zzzznotarealcountry</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open News
-2. Click the 'Saved Search' tab
-3. Verify at least one saved-search entry is listed</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The 'Saved Search' tab rendered its saved-search list area.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The Saved Search tab renders its list area</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>News_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA News</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Switching region tabs hides out-of-region countries</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on News.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open News
-2. Click the 'Europe' region tab
-3. Verify 'Australia' is no longer listed</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'Europe' hid 'Australia' from the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Australia' is not listed under 'Europe'</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>News_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA News</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Country search shows a 'no match' message for a bogus name</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on News.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Search term: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open News
 2. Search for 'zzzznotarealcountry'
 3. Verify the 'No countries found' message is shown</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Searching for a bogus country name correctly showed the 'No countries found' message.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA News/WTA News_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>News_03</t>
+          <t>News_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The 'Saved Search' tab lists pre-existing saved searches</t>
+          <t>News module loads with its tabs and placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
+          <t>The page must show the 'News Timeline'/'Saved Search' tabs and the left-panel instruction text.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on News.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -543,23 +543,22 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open News
-2. Click the 'Saved Search' tab
-3. Verify at least one saved-search entry is listed</t>
+2. Verify the tabs and placeholder are visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Saved Search' tab must show at least one previously saved search name (read-only reference data from prior sessions).</t>
+          <t>The page must show the 'News Timeline'/'Saved Search' tabs and the left-panel instruction text.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The 'Saved Search' tab rendered its saved-search list area.</t>
+          <t>The News module loaded on /wta/News with both tabs and the placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The Saved Search tab renders its list area</t>
+          <t>[PASS] News module loaded on /wta/News with its tabs and placeholder visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>News_04</t>
+          <t>News_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,12 +580,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching region tabs hides out-of-region countries</t>
+          <t>Selecting a jurisdiction renders real news articles</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
+          <t>Checking 'Australia' must render 'News of Australia between ...' with at least one actual news article and its 'Add to Project' button - unlike Pillar 2 &gt; News, Australia genuinely has news in this module.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,91 +595,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open News
-2. Click the 'Europe' region tab
-3. Verify 'Australia' is no longer listed</t>
+2. Check 'Australia'
+3. Verify the date-range text and at least one 'Add to Project' button are visible</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
+          <t>Checking 'Australia' must render 'News of Australia between ...' with at least one actual news article and its 'Add to Project' button - unlike Pillar 2 &gt; News, Australia genuinely has news in this module.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Switching to 'Europe' hid 'Australia' from the jurisdiction list.</t>
+          <t>Selecting Australia rendered 17 news article(s), each with an 'Add to Project' action.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Australia' is not listed under 'Europe'</t>
+          <t>[PASS] News of Australia renders real articles with an 'Add to Project' action</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>News_05</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA News</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Country search shows a 'no match' message for a bogus name</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on News.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Search term: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open News
-2. Search for 'zzzznotarealcountry'
-3. Verify the 'No countries found' message is shown</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a bogus country name correctly showed the 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
